--- a/Result/profitability/3234.xlsx
+++ b/Result/profitability/3234.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM71"/>
+  <dimension ref="A1:AM72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.73</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.24125</v>
+        <v>-0.19875</v>
       </c>
       <c r="N2" t="n">
-        <v>12.6825</v>
+        <v>14.30125</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.39</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.1299999999999999</v>
+        <v>-0.09499999999999995</v>
       </c>
       <c r="N3" t="n">
-        <v>14.675</v>
+        <v>16.165</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.1</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.06249999999999994</v>
+        <v>-0.09124999999999996</v>
       </c>
       <c r="N4" t="n">
-        <v>16.1675</v>
+        <v>14.95625</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.38</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.02374999999999995</v>
+        <v>0.02500000000000005</v>
       </c>
       <c r="N5" t="n">
-        <v>16.07</v>
+        <v>17.46</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.17</v>
       </c>
       <c r="M6" t="n">
-        <v>0.06625000000000006</v>
+        <v>0.1037500000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>17.95875</v>
+        <v>20.13125</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.44</v>
       </c>
       <c r="M7" t="n">
-        <v>0.17875</v>
+        <v>0.2162500000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>20.84375</v>
+        <v>22.27375</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3062500000000001</v>
+        <v>0.32625</v>
       </c>
       <c r="N8" t="n">
-        <v>23.13875</v>
+        <v>24.3925</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9445,6 +9445,133 @@
       </c>
       <c r="AM71" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>3234</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>196</v>
+      </c>
+      <c r="D72" t="n">
+        <v>157</v>
+      </c>
+      <c r="E72" t="n">
+        <v>39</v>
+      </c>
+      <c r="F72" t="n">
+        <v>19.82</v>
+      </c>
+      <c r="G72" t="n">
+        <v>-17</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>-8.70%</t>
+        </is>
+      </c>
+      <c r="I72" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J72" t="n">
+        <v>-18</v>
+      </c>
+      <c r="K72" t="n">
+        <v>-17</v>
+      </c>
+      <c r="L72" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="M72" t="n">
+        <v>-0.3525</v>
+      </c>
+      <c r="N72" t="n">
+        <v>11.67625</v>
+      </c>
+      <c r="O72" t="n">
+        <v>1</v>
+      </c>
+      <c r="P72" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>0</v>
+      </c>
+      <c r="R72" t="n">
+        <v>0</v>
+      </c>
+      <c r="S72" t="n">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>0</v>
+      </c>
+      <c r="U72" t="n">
+        <v>0</v>
+      </c>
+      <c r="V72" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W72" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="X72" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="Y72" t="n">
+        <v>10.03</v>
+      </c>
+      <c r="Z72" t="n">
+        <v>1.024514811031665</v>
+      </c>
+      <c r="AA72" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AB72" t="n">
+        <v>-0.7090909090909091</v>
+      </c>
+      <c r="AC72" t="n">
+        <v>11.12</v>
+      </c>
+      <c r="AD72" t="n">
+        <v>1.27816091954023</v>
+      </c>
+      <c r="AE72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK72" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL72" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM72" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
